--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_financial_svcs_non_bank_insurance.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.277</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="E2">
-        <v>0.402</v>
+        <v>0.5379999999999999</v>
       </c>
       <c r="G2">
-        <v>0.6011904761904762</v>
+        <v>0.670189393939394</v>
       </c>
       <c r="H2">
-        <v>0.6011904761904762</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I2">
-        <v>0.5880952380952381</v>
+        <v>0.6515151515151515</v>
       </c>
       <c r="J2">
-        <v>0.5349462054325277</v>
+        <v>0.5587121212121212</v>
       </c>
       <c r="K2">
-        <v>8.98</v>
+        <v>14.7</v>
       </c>
       <c r="L2">
-        <v>0.5345238095238095</v>
+        <v>0.5568181818181818</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -639,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.05332185234529718</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="AB2">
-        <v>0.05332185234529718</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -692,28 +692,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.277</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="E3">
-        <v>0.402</v>
+        <v>0.5379999999999999</v>
       </c>
       <c r="G3">
-        <v>0.6011904761904762</v>
+        <v>0.670189393939394</v>
       </c>
       <c r="H3">
-        <v>0.6011904761904762</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I3">
-        <v>0.5880952380952381</v>
+        <v>0.6515151515151515</v>
       </c>
       <c r="J3">
-        <v>0.5349462054325277</v>
+        <v>0.5587121212121212</v>
       </c>
       <c r="K3">
-        <v>8.98</v>
+        <v>14.7</v>
       </c>
       <c r="L3">
-        <v>0.5345238095238095</v>
+        <v>0.5568181818181818</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.05332185234529718</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="AB3">
-        <v>0.05332185234529718</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="AD3">
         <v>0</v>
